--- a/Design Files/Relay Driver-10A-v1.0/BOM/Client-BOM-Relay Driver-10A-v1.0.xlsx
+++ b/Design Files/Relay Driver-10A-v1.0/BOM/Client-BOM-Relay Driver-10A-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="376">
   <si>
     <t>#</t>
   </si>
@@ -393,9 +393,6 @@
     <t>TVS DIODE 5V 9.8V SOD923</t>
   </si>
   <si>
-    <t>TVS SURGE PROTECTOR 1-CH 3.3V</t>
-  </si>
-  <si>
     <t>TVS DIODE 5VWM 6.3VC DSN0603-2</t>
   </si>
   <si>
@@ -597,9 +594,6 @@
     <t>SOD-923.</t>
   </si>
   <si>
-    <t>SOD-123</t>
-  </si>
-  <si>
     <t>DSN0603-2</t>
   </si>
   <si>
@@ -750,9 +744,6 @@
     <t>ESD9L5.0ST5G</t>
   </si>
   <si>
-    <t>AZ3003-01G</t>
-  </si>
-  <si>
     <t>PESD5V0H1BSFYL</t>
   </si>
   <si>
@@ -924,9 +915,6 @@
     <t>ON Semiconductor</t>
   </si>
   <si>
-    <t>Amazing</t>
-  </si>
-  <si>
     <t>Nexperia</t>
   </si>
   <si>
@@ -1150,6 +1138,15 @@
   </si>
   <si>
     <t>Ralec</t>
+  </si>
+  <si>
+    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
+    <t>SD03</t>
   </si>
 </sst>
 </file>
@@ -1369,9 +1366,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1380,6 +1374,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1692,9 +1689,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1711,22 +1708,22 @@
         <v>104</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>369</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1745,16 +1742,16 @@
         <v>105</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J3" s="7">
         <v>14</v>
@@ -1777,16 +1774,16 @@
         <v>106</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="J4" s="9">
         <v>2</v>
@@ -1809,16 +1806,16 @@
         <v>107</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J5" s="7">
         <v>2</v>
@@ -1841,16 +1838,16 @@
         <v>108</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="J6" s="9">
         <v>1</v>
@@ -1873,16 +1870,16 @@
         <v>109</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -1905,16 +1902,16 @@
         <v>110</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="J8" s="9">
         <v>6</v>
@@ -1930,29 +1927,29 @@
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="J9" s="15">
+      <c r="F9" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J9" s="14">
         <v>2</v>
       </c>
-      <c r="K9" s="17" t="s">
-        <v>375</v>
+      <c r="K9" s="16" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1971,16 +1968,16 @@
         <v>111</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -2003,16 +2000,16 @@
         <v>112</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="J11" s="7">
         <v>2</v>
@@ -2035,16 +2032,16 @@
         <v>113</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J12" s="9">
         <v>4</v>
@@ -2067,16 +2064,16 @@
         <v>114</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -2099,16 +2096,16 @@
         <v>115</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="J14" s="9">
         <v>7</v>
@@ -2131,16 +2128,16 @@
         <v>116</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J15" s="7">
         <v>1</v>
@@ -2163,16 +2160,16 @@
         <v>117</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="J16" s="9">
         <v>2</v>
@@ -2188,29 +2185,29 @@
       <c r="C17" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="J17" s="15">
+      <c r="F17" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J17" s="14">
         <v>8</v>
       </c>
-      <c r="K17" s="17" t="s">
-        <v>375</v>
+      <c r="K17" s="16" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2229,16 +2226,16 @@
         <v>119</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="J18" s="9">
         <v>2</v>
@@ -2261,16 +2258,16 @@
         <v>120</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J19" s="7">
         <v>3</v>
@@ -2293,16 +2290,16 @@
         <v>121</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J20" s="9">
         <v>2</v>
@@ -2325,16 +2322,16 @@
         <v>122</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -2357,23 +2354,23 @@
         <v>123</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J22" s="9">
         <v>2</v>
       </c>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="11">
         <f>ROW(B23) - ROW($B$2)</f>
@@ -2385,20 +2382,20 @@
       <c r="D23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>301</v>
+      <c r="E23" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J23" s="7">
         <v>2</v>
@@ -2418,19 +2415,19 @@
         <v>44</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J24" s="9">
         <v>1</v>
@@ -2450,19 +2447,19 @@
         <v>45</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J25" s="7">
         <v>6</v>
@@ -2482,19 +2479,19 @@
         <v>46</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J26" s="9">
         <v>6</v>
@@ -2514,19 +2511,19 @@
         <v>47</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J27" s="7">
         <v>2</v>
@@ -2546,19 +2543,19 @@
         <v>48</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G28" s="10">
         <v>1715721</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J28" s="9">
         <v>5</v>
@@ -2578,19 +2575,19 @@
         <v>49</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F29" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="J29" s="7">
         <v>1</v>
@@ -2610,19 +2607,19 @@
         <v>50</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J30" s="9">
         <v>1</v>
@@ -2642,19 +2639,19 @@
         <v>51</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J31" s="7">
         <v>1</v>
@@ -2674,15 +2671,15 @@
         <v>52</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="9"/>
       <c r="I32" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J32" s="9">
         <v>1</v>
@@ -2702,19 +2699,19 @@
         <v>53</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J33" s="7">
         <v>1</v>
@@ -2734,19 +2731,19 @@
         <v>54</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J34" s="9">
         <v>16</v>
@@ -2766,19 +2763,19 @@
         <v>55</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="I35" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="J35" s="7">
         <v>2</v>
@@ -2798,19 +2795,19 @@
         <v>56</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="I36" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="J36" s="9">
         <v>1</v>
@@ -2830,19 +2827,19 @@
         <v>57</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="I37" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="J37" s="7">
         <v>1</v>
@@ -2862,19 +2859,19 @@
         <v>58</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F38" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="I38" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="J38" s="9">
         <v>1</v>
@@ -2894,19 +2891,19 @@
         <v>59</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F39" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I39" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="J39" s="7">
         <v>4</v>
@@ -2926,19 +2923,19 @@
         <v>60</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G40" s="10">
         <v>447690401</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J40" s="9">
         <v>16</v>
@@ -2958,19 +2955,19 @@
         <v>61</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F41" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="I41" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="J41" s="7">
         <v>16</v>
@@ -2990,19 +2987,19 @@
         <v>62</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="J42" s="9">
         <v>1</v>
@@ -3022,19 +3019,19 @@
         <v>63</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J43" s="7">
         <v>1</v>
@@ -3054,19 +3051,19 @@
         <v>64</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J44" s="9">
         <v>4</v>
@@ -3086,19 +3083,19 @@
         <v>65</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J45" s="7">
         <v>1</v>
@@ -3118,19 +3115,19 @@
         <v>66</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J46" s="9">
         <v>16</v>
@@ -3150,19 +3147,19 @@
         <v>67</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J47" s="7">
         <v>1</v>
@@ -3182,19 +3179,19 @@
         <v>68</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="J48" s="9">
         <v>1</v>
@@ -3214,19 +3211,19 @@
         <v>69</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="J49" s="7">
         <v>1</v>
@@ -3246,19 +3243,19 @@
         <v>70</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J50" s="9">
         <v>1</v>
@@ -3278,19 +3275,19 @@
         <v>71</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J51" s="7">
         <v>17</v>
@@ -3310,19 +3307,19 @@
         <v>72</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J52" s="9">
         <v>1</v>
@@ -3342,19 +3339,19 @@
         <v>73</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J53" s="7">
         <v>1</v>
@@ -3370,29 +3367,29 @@
       <c r="C54" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="H54" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="I54" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="J54" s="15">
+      <c r="E54" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J54" s="14">
         <v>2</v>
       </c>
-      <c r="K54" s="17" t="s">
-        <v>375</v>
+      <c r="K54" s="16" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3408,19 +3405,19 @@
         <v>75</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J55" s="7">
         <v>2</v>
@@ -3440,19 +3437,19 @@
         <v>76</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J56" s="9">
         <v>1</v>
@@ -3472,19 +3469,19 @@
         <v>77</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J57" s="7">
         <v>2</v>
@@ -3504,19 +3501,19 @@
         <v>78</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J58" s="9">
         <v>11</v>
@@ -3536,19 +3533,19 @@
         <v>79</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
@@ -3568,19 +3565,19 @@
         <v>80</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J60" s="9">
         <v>2</v>
@@ -3600,19 +3597,19 @@
         <v>81</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J61" s="7">
         <v>1</v>
@@ -3632,19 +3629,19 @@
         <v>82</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J62" s="9">
         <v>13</v>
@@ -3664,19 +3661,19 @@
         <v>83</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J63" s="7">
         <v>6</v>
@@ -3696,19 +3693,19 @@
         <v>84</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J64" s="9">
         <v>2</v>
@@ -3728,19 +3725,19 @@
         <v>85</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J65" s="7">
         <v>2</v>
@@ -3760,19 +3757,19 @@
         <v>86</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J66" s="9">
         <v>1</v>
@@ -3788,29 +3785,29 @@
       <c r="C67" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E67" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="I67" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="J67" s="15">
+      <c r="E67" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="G67" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="I67" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J67" s="14">
         <v>1</v>
       </c>
-      <c r="K67" s="17" t="s">
-        <v>375</v>
+      <c r="K67" s="16" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3826,19 +3823,19 @@
         <v>88</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J68" s="9">
         <v>8</v>
@@ -3858,19 +3855,19 @@
         <v>89</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J69" s="7">
         <v>2</v>
@@ -3890,19 +3887,19 @@
         <v>90</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J70" s="9">
         <v>2</v>
@@ -3922,19 +3919,19 @@
         <v>91</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F71" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="I71" s="8" t="s">
         <v>370</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>374</v>
       </c>
       <c r="J71" s="7">
         <v>2</v>
@@ -3954,19 +3951,19 @@
         <v>92</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J72" s="9">
         <v>1</v>
@@ -3986,19 +3983,19 @@
         <v>93</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J73" s="7">
         <v>1</v>
@@ -4018,19 +4015,19 @@
         <v>94</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J74" s="9">
         <v>1</v>
@@ -4050,19 +4047,19 @@
         <v>95</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J75" s="7">
         <v>1</v>
@@ -4082,19 +4079,19 @@
         <v>96</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
@@ -4114,19 +4111,19 @@
         <v>97</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J77" s="7">
         <v>2</v>
@@ -4146,19 +4143,19 @@
         <v>98</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J78" s="9">
         <v>1</v>
@@ -4178,19 +4175,19 @@
         <v>99</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J79" s="7">
         <v>1</v>
@@ -4210,19 +4207,19 @@
         <v>100</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J80" s="9">
         <v>3</v>
@@ -4238,29 +4235,29 @@
       <c r="C81" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D81" s="15" t="s">
+      <c r="D81" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E81" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F81" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="G81" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="H81" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="I81" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="J81" s="15">
+      <c r="E81" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F81" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="G81" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="I81" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J81" s="14">
         <v>1</v>
       </c>
-      <c r="K81" s="17" t="s">
-        <v>375</v>
+      <c r="K81" s="16" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4276,19 +4273,19 @@
         <v>102</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J82" s="9">
         <v>1</v>
@@ -4308,19 +4305,19 @@
         <v>103</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J83" s="7">
         <v>1</v>

--- a/Design Files/Relay Driver-10A-v1.0/BOM/Client-BOM-Relay Driver-10A-v1.0.xlsx
+++ b/Design Files/Relay Driver-10A-v1.0/BOM/Client-BOM-Relay Driver-10A-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -328,6 +328,21 @@
   </si>
   <si>
     <t>16-SOIC</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>0287001.PXCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 1A Automotive Fuses ROHS</t>
   </si>
 </sst>
 </file>
@@ -820,7 +835,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -830,7 +845,7 @@
     <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -916,7 +931,7 @@
     <row r="4" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B20" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B21" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -1418,7 +1433,7 @@
         <v>92</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -1450,12 +1465,43 @@
         <v>93</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
       </c>
       <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="11">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J21" s="9">
+        <v>1</v>
+      </c>
+      <c r="K21" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
